--- a/manuscript/lichen_dong_within_rge_supplemental_tables.xlsx
+++ b/manuscript/lichen_dong_within_rge_supplemental_tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repo\2024_within_fam_rge\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6556FE73-6D52-4135-B176-AAF66722441E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726D27F5-24E5-4DC1-8FC1-93B976E4067C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="18720" windowHeight="11690" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,6 @@
     <sheet name="Table 2" sheetId="5" r:id="rId3"/>
     <sheet name="Table 3" sheetId="6" r:id="rId4"/>
     <sheet name="Table 4" sheetId="7" r:id="rId5"/>
-    <sheet name="Table 5" sheetId="8" r:id="rId6"/>
-    <sheet name="Table 6" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="100">
   <si>
     <t>Table of Contents</t>
   </si>
@@ -331,108 +329,6 @@
   </si>
   <si>
     <t>Both items assess attitutdes towards teachers.</t>
-  </si>
-  <si>
-    <t>Wave 1</t>
-  </si>
-  <si>
-    <t>H1TO15</t>
-  </si>
-  <si>
-    <t>H1TO17</t>
-  </si>
-  <si>
-    <t>H1TO5</t>
-  </si>
-  <si>
-    <t>H1TO32</t>
-  </si>
-  <si>
-    <t>H1TO36</t>
-  </si>
-  <si>
-    <t>H1TO42</t>
-  </si>
-  <si>
-    <t>During the past 12 months, how often did you drink beer, wine, or liquor?</t>
-  </si>
-  <si>
-    <t>Over the past 12 months, on how many days did you drink 5 or more drinks in a row?</t>
-  </si>
-  <si>
-    <t>During the past 30 days, on how many days did you smoke cigarettes?</t>
-  </si>
-  <si>
-    <t>During the past 30 days, how many times did you use marijuana?</t>
-  </si>
-  <si>
-    <t>During the past 30 days, how many times did you use cocaine?</t>
-  </si>
-  <si>
-    <t>During the past 30 days, how many times did you use any of these types of illegal drugs? (LSD, PCP, ecstasy, mushrooms, speed, ice, heroin, or pills)</t>
-  </si>
-  <si>
-    <t>H1DS2</t>
-  </si>
-  <si>
-    <t>H1DS12</t>
-  </si>
-  <si>
-    <t>H1FV8</t>
-  </si>
-  <si>
-    <t>H1DS6</t>
-  </si>
-  <si>
-    <t>H1DS9</t>
-  </si>
-  <si>
-    <t>H1DS10</t>
-  </si>
-  <si>
-    <t>H1DS13</t>
-  </si>
-  <si>
-    <t>H1DS11</t>
-  </si>
-  <si>
-    <t>H1FV7</t>
-  </si>
-  <si>
-    <t>H1DS7</t>
-  </si>
-  <si>
-    <t>In the past 12 months, how often did you deliberately damage property that didn't belong to you?</t>
-  </si>
-  <si>
-    <t>How often did you sell marijuana or other drugs?</t>
-  </si>
-  <si>
-    <t>During the past 12 months, did the following happen? If so, how often? You shot or stabbed someone.</t>
-  </si>
-  <si>
-    <t>In the past 12 months, how often did you hurt someone badly enough to need bandages or care from a doctor or nurse?</t>
-  </si>
-  <si>
-    <t>In the past 12 months, how often did you steal something worth more than $50?</t>
-  </si>
-  <si>
-    <t>How often did you go into a house or building to steal something?</t>
-  </si>
-  <si>
-    <t>How often did you steal something worth less than $50?</t>
-  </si>
-  <si>
-    <t>How often did you use or threaten to use a weapon to get something from someone?</t>
-  </si>
-  <si>
-    <t>Have you ever run away from home? If so, how often?</t>
-  </si>
-  <si>
-    <t>During the past 12 months, did the following happen? If so, how often? You pulled a knife or gun on someone.</t>
-  </si>
-  <si>
-    <t>ASB</t>
   </si>
 </sst>
 </file>
@@ -2094,530 +1990,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906ED566-CD89-4F49-A406-43CF327E2066}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
-    <col min="7" max="7" width="112" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.90900000000000003</v>
-      </c>
-      <c r="D3" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="G3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="5"/>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.93799999999999994</v>
-      </c>
-      <c r="D4" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.88</v>
-      </c>
-      <c r="G4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-      <c r="B5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="D5" s="2">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.45500000000000002</v>
-      </c>
-      <c r="G5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
-      <c r="B6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.76100000000000001</v>
-      </c>
-      <c r="D6" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.57799999999999996</v>
-      </c>
-      <c r="G6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="5"/>
-      <c r="B7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0.69699999999999995</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.48599999999999999</v>
-      </c>
-      <c r="G7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="5"/>
-      <c r="B8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.80600000000000005</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="G8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>7.3999999999999996E-2</v>
-      </c>
-      <c r="B12">
-        <v>0.97099999999999997</v>
-      </c>
-      <c r="C12">
-        <v>0.95899999999999996</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:A8"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{426FEDD9-F3E0-46A3-85E7-D236B5300FBA}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
-    <col min="7" max="7" width="112" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.68700000000000006</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1.2E-2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.47199999999999998</v>
-      </c>
-      <c r="G3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="5"/>
-      <c r="B4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.71899999999999997</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1.4E-2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.51700000000000002</v>
-      </c>
-      <c r="G4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-      <c r="B5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.89300000000000002</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1.6E-2</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.79700000000000004</v>
-      </c>
-      <c r="G5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
-      <c r="B6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.63500000000000001</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="G6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="5"/>
-      <c r="B7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0.82699999999999996</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1.2E-2</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.68400000000000005</v>
-      </c>
-      <c r="G7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="5"/>
-      <c r="B8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.82399999999999995</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="G8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="5"/>
-      <c r="B9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.71699999999999997</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1.2E-2</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.51400000000000001</v>
-      </c>
-      <c r="G9" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="5"/>
-      <c r="B10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.76400000000000001</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.184</v>
-      </c>
-      <c r="G10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="5"/>
-      <c r="B11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.83899999999999997</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1.2E-2</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.70399999999999996</v>
-      </c>
-      <c r="G11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="5"/>
-      <c r="B12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.47299999999999998</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.224</v>
-      </c>
-      <c r="G12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="B16">
-        <v>0.94099999999999995</v>
-      </c>
-      <c r="C16">
-        <v>0.92900000000000005</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:A12"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>